--- a/组内贡献分配表.xlsx
+++ b/组内贡献分配表.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="3">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="F3" s="7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="4">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="5">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="F5" s="7" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="6">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="7">
